--- a/docs/Calculations.xlsx
+++ b/docs/Calculations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\gordon\ecvs\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{138051CA-AB87-4B30-9E00-DE9404EDD283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DBCB31-3D58-47D3-9B71-E7AE0CFC2CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{6F13BD72-AB9A-465E-85B8-5B5C60C98C53}"/>
+    <workbookView xWindow="19110" yWindow="-5070" windowWidth="27170" windowHeight="20970" xr2:uid="{6F13BD72-AB9A-465E-85B8-5B5C60C98C53}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Pantheon Height</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Y Resolution</t>
+  </si>
+  <si>
+    <t>fixed</t>
   </si>
 </sst>
 </file>
@@ -533,6 +536,11 @@
         <v>368.64</v>
       </c>
     </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>2</v>
@@ -546,6 +554,9 @@
       <c r="D11">
         <v>15</v>
       </c>
+      <c r="E11">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -563,6 +574,10 @@
         <f t="shared" si="0"/>
         <v>33.541019662496844</v>
       </c>
+      <c r="E12">
+        <f t="shared" ref="E12" si="1">SQRT(($B$3*$B$3)+(E11*E11))</f>
+        <v>33.541019662496844</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -573,12 +588,15 @@
         <v>80.537677791974389</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:D13" si="1">DEGREES(ASIN($B$3/C12))</f>
+        <f t="shared" ref="C13:D13" si="2">DEGREES(ASIN($B$3/C12))</f>
         <v>71.565051177077976</v>
       </c>
       <c r="D13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>63.434948822922017</v>
+      </c>
+      <c r="E13">
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -590,12 +608,16 @@
         <v>0.21847243324645832</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:D14" si="2">C13/$C$9</f>
+        <f t="shared" ref="C14:D14" si="3">C13/$C$9</f>
         <v>0.19413262580587559</v>
       </c>
       <c r="D14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.17207831169412441</v>
+      </c>
+      <c r="E14">
+        <f t="shared" ref="E14" si="4">E13/$C$9</f>
+        <v>0.1980251736111111</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -607,11 +629,15 @@
         <v>9.9333333333333329E-2</v>
       </c>
       <c r="C15">
-        <f t="shared" ref="C15:D15" si="3">C11*$B$1/$B$3</f>
+        <f t="shared" ref="C15:D15" si="5">C11*$B$1/$B$3</f>
         <v>0.19866666666666666</v>
       </c>
       <c r="D15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="E15">
+        <f t="shared" ref="E15" si="6">E11*$B$1/$B$3</f>
         <v>0.29799999999999999</v>
       </c>
     </row>
